--- a/Na-aba/home/test.xlsx
+++ b/Na-aba/home/test.xlsx
@@ -1,49 +1,161 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건협의체 회의자료" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건교육 이수 관리대장" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'표지'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'안전보건교육 이수 관리대장'!$A$1:$AD$30</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Val</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="14">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="004472C4"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="32"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -51,18 +163,227 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="001F4E79"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="39">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -350,23 +671,1792 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B7:C37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="1" ht="19.5" customHeight="1"/>
+    <row r="2" ht="19.5" customHeight="1"/>
+    <row r="3" ht="19.5" customHeight="1"/>
+    <row r="4" ht="19.5" customHeight="1"/>
+    <row r="5" ht="19.5" customHeight="1"/>
+    <row r="6" ht="19.5" customHeight="1"/>
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>「가산~가평 천연가스 공급시설 건설공사」</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>안전  및  보건에  관한  협의체  회의자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1"/>
+    <row r="13" ht="19.5" customHeight="1"/>
+    <row r="14" ht="19.5" customHeight="1"/>
+    <row r="15" ht="19.5" customHeight="1"/>
+    <row r="16" ht="19.5" customHeight="1"/>
+    <row r="17" ht="19.5" customHeight="1"/>
+    <row r="18" ht="19.5" customHeight="1"/>
+    <row r="19" ht="19.5" customHeight="1"/>
+    <row r="20" ht="19.5" customHeight="1"/>
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1"/>
+    <row r="23" ht="19.5" customHeight="1"/>
+    <row r="24" ht="19.5" customHeight="1"/>
+    <row r="25" ht="19.5" customHeight="1"/>
+    <row r="26" ht="19.5" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1"/>
+    <row r="28" ht="19.5" customHeight="1"/>
+    <row r="29" ht="19.5" customHeight="1"/>
+    <row r="30" ht="19.5" customHeight="1"/>
+    <row r="31" ht="19.5" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1"/>
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="34" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>수급업체명</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>서울검사(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>제  출  년  월</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19.5" customHeight="1"/>
+    <row r="39" ht="19.5" customHeight="1"/>
+    <row r="40" ht="19.5" customHeight="1"/>
+    <row r="41" ht="19.5" customHeight="1"/>
+    <row r="42" ht="19.5" customHeight="1"/>
+    <row r="43" ht="19.5" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>가산~가평 천연가스 공급시설 건설공사</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026년 7월 안전 및 보건에 관한 협의체 회의자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>수급업체명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>서울검사(주)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>제 출 년 월</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>2026년 7월</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>1. 수급업체 현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>계 약 명</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>계약기간</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>계약상대자(업체명)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>서울검사(주)</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>작업의 시작시간</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>작업 또는 작업장 간의 연락방법</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="12" t="inlineStr"/>
+      <c r="D14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>재해발생 위험시의 대피방법</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="12" t="inlineStr"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>사업자와 수급인 또는 수급인 상호간의 연락방법
+현장소장 및 안전관리자 핫라인 구축</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>작업공정의 조정 및 협의 요청사항</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="12" t="inlineStr"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="55" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026년 6월
+주요 활동실적
+(작업사항)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026년 7월
+주요 활동계획
+(작업사항)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="12" t="inlineStr"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2. 위험성평가 실시 현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>실시여부(O,X)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>작성 날짜</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>최초 위험성평가</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="10" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>계약당시 전체 작업 대상 작성</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>정기 위험성평가</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="10" t="inlineStr"/>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>매년 당해연도 전체 작업 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>수시위험성평가</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>매월 협의체 회의시 제출</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:B9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AD30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="26" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="6" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>'26년  2026년 7월  수급업체 안전보건교육 이수 관리대장</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>- 수급업체명 :</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>서울검사(주)</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>- 계  약  명 :</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>본인(현장대리인)은 당사 근로자에 대한 산업안전보건법상의 안전보건교육을 철저히 이행하였음을 확인합니다.</t>
+        </is>
+      </c>
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t>현장대리인 :</t>
+        </is>
+      </c>
+      <c r="X3" s="17" t="inlineStr"/>
+      <c r="AC3" s="16" t="inlineStr">
+        <is>
+          <t>(인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>성  명</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>업무형태 구분 Check:</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>채용일자
+(최초투입일)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>채용·시교육이수현황Check:</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>근로자 특별안전·보건교육
+[일용(단기)&amp;강별]:2시간  그 외:16시간</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="20" t="n"/>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>1분기 (시간)</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="20" t="n"/>
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t>2분기 (시간)</t>
+        </is>
+      </c>
+      <c r="P4" s="20" t="n"/>
+      <c r="Q4" s="20" t="n"/>
+      <c r="R4" s="24" t="inlineStr">
+        <is>
+          <t>3분기 (시간)</t>
+        </is>
+      </c>
+      <c r="S4" s="20" t="n"/>
+      <c r="T4" s="20" t="n"/>
+      <c r="U4" s="25" t="inlineStr">
+        <is>
+          <t>4분기 (시간)</t>
+        </is>
+      </c>
+      <c r="V4" s="20" t="n"/>
+      <c r="W4" s="20" t="n"/>
+      <c r="X4" s="26" t="inlineStr">
+        <is>
+          <t>관리감독자
+연간 16시간</t>
+        </is>
+      </c>
+      <c r="Y4" s="20" t="n"/>
+      <c r="Z4" s="27" t="inlineStr">
+        <is>
+          <t>작업(근로)자
+매반기 12시간</t>
+        </is>
+      </c>
+      <c r="AA4" s="20" t="n"/>
+      <c r="AB4" s="20" t="n"/>
+      <c r="AC4" s="20" t="n"/>
+      <c r="AD4" s="18" t="inlineStr">
+        <is>
+          <t>비  고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>작업(근로)자/관리감독자</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>일용
+1시간</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>일용 외
+8시간</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>대상여부
+Check</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="n"/>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>교육이수일
+[이수사대]</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="N5" s="22" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="O5" s="23" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="P5" s="23" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="R5" s="24" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="S5" s="24" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="U5" s="25" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="V5" s="25" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="W5" s="25" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="X5" s="26" t="inlineStr">
+        <is>
+          <t>매반</t>
+        </is>
+      </c>
+      <c r="Y5" s="26" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="Z5" s="27" t="inlineStr">
+        <is>
+          <t>매반</t>
+        </is>
+      </c>
+      <c r="AA5" s="27" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="AB5" s="27" t="inlineStr">
+        <is>
+          <t>매반</t>
+        </is>
+      </c>
+      <c r="AC5" s="27" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="AD5" s="20" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="20" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>작업
+(근로)자</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>관리감독자
+상용</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>관리감독자
+임용</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>비대상
+(작업명)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
+      <c r="P6" s="20" t="n"/>
+      <c r="Q6" s="20" t="n"/>
+      <c r="R6" s="20" t="n"/>
+      <c r="S6" s="20" t="n"/>
+      <c r="T6" s="20" t="n"/>
+      <c r="U6" s="20" t="n"/>
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="20" t="n"/>
+      <c r="X6" s="20" t="n"/>
+      <c r="Y6" s="20" t="n"/>
+      <c r="Z6" s="20" t="n"/>
+      <c r="AA6" s="20" t="n"/>
+      <c r="AB6" s="20" t="n"/>
+      <c r="AC6" s="20" t="n"/>
+      <c r="AD6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="28" t="n">
         <v>1</v>
       </c>
+      <c r="B7" s="28" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="29" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr"/>
+      <c r="H7" s="29" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+      <c r="K7" s="30" t="inlineStr"/>
+      <c r="L7" s="31" t="inlineStr"/>
+      <c r="M7" s="31" t="inlineStr"/>
+      <c r="N7" s="31" t="inlineStr"/>
+      <c r="O7" s="32" t="inlineStr"/>
+      <c r="P7" s="32" t="inlineStr"/>
+      <c r="Q7" s="32" t="inlineStr"/>
+      <c r="R7" s="33" t="inlineStr"/>
+      <c r="S7" s="33" t="inlineStr"/>
+      <c r="T7" s="33" t="inlineStr"/>
+      <c r="U7" s="34" t="inlineStr"/>
+      <c r="V7" s="34" t="inlineStr"/>
+      <c r="W7" s="34" t="inlineStr"/>
+      <c r="X7" s="35" t="inlineStr"/>
+      <c r="Y7" s="35" t="inlineStr"/>
+      <c r="Z7" s="36" t="inlineStr"/>
+      <c r="AA7" s="36" t="inlineStr"/>
+      <c r="AB7" s="36" t="inlineStr"/>
+      <c r="AC7" s="36" t="inlineStr"/>
+      <c r="AD7" s="37" t="inlineStr"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="20" t="n"/>
+      <c r="B8" s="29" t="inlineStr"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
+      <c r="P8" s="20" t="n"/>
+      <c r="Q8" s="20" t="n"/>
+      <c r="R8" s="20" t="n"/>
+      <c r="S8" s="20" t="n"/>
+      <c r="T8" s="20" t="n"/>
+      <c r="U8" s="20" t="n"/>
+      <c r="V8" s="20" t="n"/>
+      <c r="W8" s="20" t="n"/>
+      <c r="X8" s="20" t="n"/>
+      <c r="Y8" s="20" t="n"/>
+      <c r="Z8" s="20" t="n"/>
+      <c r="AA8" s="20" t="n"/>
+      <c r="AB8" s="20" t="n"/>
+      <c r="AC8" s="20" t="n"/>
+      <c r="AD8" s="20" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="29" t="inlineStr"/>
+      <c r="G9" s="29" t="inlineStr"/>
+      <c r="H9" s="29" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
+      <c r="K9" s="30" t="inlineStr"/>
+      <c r="L9" s="31" t="inlineStr"/>
+      <c r="M9" s="31" t="inlineStr"/>
+      <c r="N9" s="31" t="inlineStr"/>
+      <c r="O9" s="32" t="inlineStr"/>
+      <c r="P9" s="32" t="inlineStr"/>
+      <c r="Q9" s="32" t="inlineStr"/>
+      <c r="R9" s="33" t="inlineStr"/>
+      <c r="S9" s="33" t="inlineStr"/>
+      <c r="T9" s="33" t="inlineStr"/>
+      <c r="U9" s="34" t="inlineStr"/>
+      <c r="V9" s="34" t="inlineStr"/>
+      <c r="W9" s="34" t="inlineStr"/>
+      <c r="X9" s="35" t="inlineStr"/>
+      <c r="Y9" s="35" t="inlineStr"/>
+      <c r="Z9" s="36" t="inlineStr"/>
+      <c r="AA9" s="36" t="inlineStr"/>
+      <c r="AB9" s="36" t="inlineStr"/>
+      <c r="AC9" s="36" t="inlineStr"/>
+      <c r="AD9" s="37" t="inlineStr"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="29" t="inlineStr"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
+      <c r="P10" s="20" t="n"/>
+      <c r="Q10" s="20" t="n"/>
+      <c r="R10" s="20" t="n"/>
+      <c r="S10" s="20" t="n"/>
+      <c r="T10" s="20" t="n"/>
+      <c r="U10" s="20" t="n"/>
+      <c r="V10" s="20" t="n"/>
+      <c r="W10" s="20" t="n"/>
+      <c r="X10" s="20" t="n"/>
+      <c r="Y10" s="20" t="n"/>
+      <c r="Z10" s="20" t="n"/>
+      <c r="AA10" s="20" t="n"/>
+      <c r="AB10" s="20" t="n"/>
+      <c r="AC10" s="20" t="n"/>
+      <c r="AD10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr"/>
+      <c r="H11" s="29" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
+      <c r="K11" s="30" t="inlineStr"/>
+      <c r="L11" s="31" t="inlineStr"/>
+      <c r="M11" s="31" t="inlineStr"/>
+      <c r="N11" s="31" t="inlineStr"/>
+      <c r="O11" s="32" t="inlineStr"/>
+      <c r="P11" s="32" t="inlineStr"/>
+      <c r="Q11" s="32" t="inlineStr"/>
+      <c r="R11" s="33" t="inlineStr"/>
+      <c r="S11" s="33" t="inlineStr"/>
+      <c r="T11" s="33" t="inlineStr"/>
+      <c r="U11" s="34" t="inlineStr"/>
+      <c r="V11" s="34" t="inlineStr"/>
+      <c r="W11" s="34" t="inlineStr"/>
+      <c r="X11" s="35" t="inlineStr"/>
+      <c r="Y11" s="35" t="inlineStr"/>
+      <c r="Z11" s="36" t="inlineStr"/>
+      <c r="AA11" s="36" t="inlineStr"/>
+      <c r="AB11" s="36" t="inlineStr"/>
+      <c r="AC11" s="36" t="inlineStr"/>
+      <c r="AD11" s="37" t="inlineStr"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="29" t="inlineStr"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="n"/>
+      <c r="O12" s="20" t="n"/>
+      <c r="P12" s="20" t="n"/>
+      <c r="Q12" s="20" t="n"/>
+      <c r="R12" s="20" t="n"/>
+      <c r="S12" s="20" t="n"/>
+      <c r="T12" s="20" t="n"/>
+      <c r="U12" s="20" t="n"/>
+      <c r="V12" s="20" t="n"/>
+      <c r="W12" s="20" t="n"/>
+      <c r="X12" s="20" t="n"/>
+      <c r="Y12" s="20" t="n"/>
+      <c r="Z12" s="20" t="n"/>
+      <c r="AA12" s="20" t="n"/>
+      <c r="AB12" s="20" t="n"/>
+      <c r="AC12" s="20" t="n"/>
+      <c r="AD12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
+      <c r="E13" s="19" t="inlineStr"/>
+      <c r="F13" s="29" t="inlineStr"/>
+      <c r="G13" s="29" t="inlineStr"/>
+      <c r="H13" s="29" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
+      <c r="K13" s="30" t="inlineStr"/>
+      <c r="L13" s="31" t="inlineStr"/>
+      <c r="M13" s="31" t="inlineStr"/>
+      <c r="N13" s="31" t="inlineStr"/>
+      <c r="O13" s="32" t="inlineStr"/>
+      <c r="P13" s="32" t="inlineStr"/>
+      <c r="Q13" s="32" t="inlineStr"/>
+      <c r="R13" s="33" t="inlineStr"/>
+      <c r="S13" s="33" t="inlineStr"/>
+      <c r="T13" s="33" t="inlineStr"/>
+      <c r="U13" s="34" t="inlineStr"/>
+      <c r="V13" s="34" t="inlineStr"/>
+      <c r="W13" s="34" t="inlineStr"/>
+      <c r="X13" s="35" t="inlineStr"/>
+      <c r="Y13" s="35" t="inlineStr"/>
+      <c r="Z13" s="36" t="inlineStr"/>
+      <c r="AA13" s="36" t="inlineStr"/>
+      <c r="AB13" s="36" t="inlineStr"/>
+      <c r="AC13" s="36" t="inlineStr"/>
+      <c r="AD13" s="37" t="inlineStr"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="29" t="inlineStr"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="20" t="n"/>
+      <c r="O14" s="20" t="n"/>
+      <c r="P14" s="20" t="n"/>
+      <c r="Q14" s="20" t="n"/>
+      <c r="R14" s="20" t="n"/>
+      <c r="S14" s="20" t="n"/>
+      <c r="T14" s="20" t="n"/>
+      <c r="U14" s="20" t="n"/>
+      <c r="V14" s="20" t="n"/>
+      <c r="W14" s="20" t="n"/>
+      <c r="X14" s="20" t="n"/>
+      <c r="Y14" s="20" t="n"/>
+      <c r="Z14" s="20" t="n"/>
+      <c r="AA14" s="20" t="n"/>
+      <c r="AB14" s="20" t="n"/>
+      <c r="AC14" s="20" t="n"/>
+      <c r="AD14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr"/>
+      <c r="E15" s="19" t="inlineStr"/>
+      <c r="F15" s="29" t="inlineStr"/>
+      <c r="G15" s="29" t="inlineStr"/>
+      <c r="H15" s="29" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
+      <c r="K15" s="30" t="inlineStr"/>
+      <c r="L15" s="31" t="inlineStr"/>
+      <c r="M15" s="31" t="inlineStr"/>
+      <c r="N15" s="31" t="inlineStr"/>
+      <c r="O15" s="32" t="inlineStr"/>
+      <c r="P15" s="32" t="inlineStr"/>
+      <c r="Q15" s="32" t="inlineStr"/>
+      <c r="R15" s="33" t="inlineStr"/>
+      <c r="S15" s="33" t="inlineStr"/>
+      <c r="T15" s="33" t="inlineStr"/>
+      <c r="U15" s="34" t="inlineStr"/>
+      <c r="V15" s="34" t="inlineStr"/>
+      <c r="W15" s="34" t="inlineStr"/>
+      <c r="X15" s="35" t="inlineStr"/>
+      <c r="Y15" s="35" t="inlineStr"/>
+      <c r="Z15" s="36" t="inlineStr"/>
+      <c r="AA15" s="36" t="inlineStr"/>
+      <c r="AB15" s="36" t="inlineStr"/>
+      <c r="AC15" s="36" t="inlineStr"/>
+      <c r="AD15" s="37" t="inlineStr"/>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="20" t="n"/>
+      <c r="B16" s="29" t="inlineStr"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="n"/>
+      <c r="O16" s="20" t="n"/>
+      <c r="P16" s="20" t="n"/>
+      <c r="Q16" s="20" t="n"/>
+      <c r="R16" s="20" t="n"/>
+      <c r="S16" s="20" t="n"/>
+      <c r="T16" s="20" t="n"/>
+      <c r="U16" s="20" t="n"/>
+      <c r="V16" s="20" t="n"/>
+      <c r="W16" s="20" t="n"/>
+      <c r="X16" s="20" t="n"/>
+      <c r="Y16" s="20" t="n"/>
+      <c r="Z16" s="20" t="n"/>
+      <c r="AA16" s="20" t="n"/>
+      <c r="AB16" s="20" t="n"/>
+      <c r="AC16" s="20" t="n"/>
+      <c r="AD16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr"/>
+      <c r="C17" s="19" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr"/>
+      <c r="E17" s="19" t="inlineStr"/>
+      <c r="F17" s="29" t="inlineStr"/>
+      <c r="G17" s="29" t="inlineStr"/>
+      <c r="H17" s="29" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
+      <c r="K17" s="30" t="inlineStr"/>
+      <c r="L17" s="31" t="inlineStr"/>
+      <c r="M17" s="31" t="inlineStr"/>
+      <c r="N17" s="31" t="inlineStr"/>
+      <c r="O17" s="32" t="inlineStr"/>
+      <c r="P17" s="32" t="inlineStr"/>
+      <c r="Q17" s="32" t="inlineStr"/>
+      <c r="R17" s="33" t="inlineStr"/>
+      <c r="S17" s="33" t="inlineStr"/>
+      <c r="T17" s="33" t="inlineStr"/>
+      <c r="U17" s="34" t="inlineStr"/>
+      <c r="V17" s="34" t="inlineStr"/>
+      <c r="W17" s="34" t="inlineStr"/>
+      <c r="X17" s="35" t="inlineStr"/>
+      <c r="Y17" s="35" t="inlineStr"/>
+      <c r="Z17" s="36" t="inlineStr"/>
+      <c r="AA17" s="36" t="inlineStr"/>
+      <c r="AB17" s="36" t="inlineStr"/>
+      <c r="AC17" s="36" t="inlineStr"/>
+      <c r="AD17" s="37" t="inlineStr"/>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="29" t="inlineStr"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="20" t="n"/>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="20" t="n"/>
+      <c r="O18" s="20" t="n"/>
+      <c r="P18" s="20" t="n"/>
+      <c r="Q18" s="20" t="n"/>
+      <c r="R18" s="20" t="n"/>
+      <c r="S18" s="20" t="n"/>
+      <c r="T18" s="20" t="n"/>
+      <c r="U18" s="20" t="n"/>
+      <c r="V18" s="20" t="n"/>
+      <c r="W18" s="20" t="n"/>
+      <c r="X18" s="20" t="n"/>
+      <c r="Y18" s="20" t="n"/>
+      <c r="Z18" s="20" t="n"/>
+      <c r="AA18" s="20" t="n"/>
+      <c r="AB18" s="20" t="n"/>
+      <c r="AC18" s="20" t="n"/>
+      <c r="AD18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr"/>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr"/>
+      <c r="E19" s="19" t="inlineStr"/>
+      <c r="F19" s="29" t="inlineStr"/>
+      <c r="G19" s="29" t="inlineStr"/>
+      <c r="H19" s="29" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
+      <c r="K19" s="30" t="inlineStr"/>
+      <c r="L19" s="31" t="inlineStr"/>
+      <c r="M19" s="31" t="inlineStr"/>
+      <c r="N19" s="31" t="inlineStr"/>
+      <c r="O19" s="32" t="inlineStr"/>
+      <c r="P19" s="32" t="inlineStr"/>
+      <c r="Q19" s="32" t="inlineStr"/>
+      <c r="R19" s="33" t="inlineStr"/>
+      <c r="S19" s="33" t="inlineStr"/>
+      <c r="T19" s="33" t="inlineStr"/>
+      <c r="U19" s="34" t="inlineStr"/>
+      <c r="V19" s="34" t="inlineStr"/>
+      <c r="W19" s="34" t="inlineStr"/>
+      <c r="X19" s="35" t="inlineStr"/>
+      <c r="Y19" s="35" t="inlineStr"/>
+      <c r="Z19" s="36" t="inlineStr"/>
+      <c r="AA19" s="36" t="inlineStr"/>
+      <c r="AB19" s="36" t="inlineStr"/>
+      <c r="AC19" s="36" t="inlineStr"/>
+      <c r="AD19" s="37" t="inlineStr"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="29" t="inlineStr"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="20" t="n"/>
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="20" t="n"/>
+      <c r="O20" s="20" t="n"/>
+      <c r="P20" s="20" t="n"/>
+      <c r="Q20" s="20" t="n"/>
+      <c r="R20" s="20" t="n"/>
+      <c r="S20" s="20" t="n"/>
+      <c r="T20" s="20" t="n"/>
+      <c r="U20" s="20" t="n"/>
+      <c r="V20" s="20" t="n"/>
+      <c r="W20" s="20" t="n"/>
+      <c r="X20" s="20" t="n"/>
+      <c r="Y20" s="20" t="n"/>
+      <c r="Z20" s="20" t="n"/>
+      <c r="AA20" s="20" t="n"/>
+      <c r="AB20" s="20" t="n"/>
+      <c r="AC20" s="20" t="n"/>
+      <c r="AD20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr"/>
+      <c r="C21" s="19" t="inlineStr"/>
+      <c r="D21" s="19" t="inlineStr"/>
+      <c r="E21" s="19" t="inlineStr"/>
+      <c r="F21" s="29" t="inlineStr"/>
+      <c r="G21" s="29" t="inlineStr"/>
+      <c r="H21" s="29" t="inlineStr"/>
+      <c r="I21" s="21" t="inlineStr"/>
+      <c r="J21" s="21" t="inlineStr"/>
+      <c r="K21" s="30" t="inlineStr"/>
+      <c r="L21" s="31" t="inlineStr"/>
+      <c r="M21" s="31" t="inlineStr"/>
+      <c r="N21" s="31" t="inlineStr"/>
+      <c r="O21" s="32" t="inlineStr"/>
+      <c r="P21" s="32" t="inlineStr"/>
+      <c r="Q21" s="32" t="inlineStr"/>
+      <c r="R21" s="33" t="inlineStr"/>
+      <c r="S21" s="33" t="inlineStr"/>
+      <c r="T21" s="33" t="inlineStr"/>
+      <c r="U21" s="34" t="inlineStr"/>
+      <c r="V21" s="34" t="inlineStr"/>
+      <c r="W21" s="34" t="inlineStr"/>
+      <c r="X21" s="35" t="inlineStr"/>
+      <c r="Y21" s="35" t="inlineStr"/>
+      <c r="Z21" s="36" t="inlineStr"/>
+      <c r="AA21" s="36" t="inlineStr"/>
+      <c r="AB21" s="36" t="inlineStr"/>
+      <c r="AC21" s="36" t="inlineStr"/>
+      <c r="AD21" s="37" t="inlineStr"/>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="29" t="inlineStr"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="20" t="n"/>
+      <c r="M22" s="20" t="n"/>
+      <c r="N22" s="20" t="n"/>
+      <c r="O22" s="20" t="n"/>
+      <c r="P22" s="20" t="n"/>
+      <c r="Q22" s="20" t="n"/>
+      <c r="R22" s="20" t="n"/>
+      <c r="S22" s="20" t="n"/>
+      <c r="T22" s="20" t="n"/>
+      <c r="U22" s="20" t="n"/>
+      <c r="V22" s="20" t="n"/>
+      <c r="W22" s="20" t="n"/>
+      <c r="X22" s="20" t="n"/>
+      <c r="Y22" s="20" t="n"/>
+      <c r="Z22" s="20" t="n"/>
+      <c r="AA22" s="20" t="n"/>
+      <c r="AB22" s="20" t="n"/>
+      <c r="AC22" s="20" t="n"/>
+      <c r="AD22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr"/>
+      <c r="C23" s="19" t="inlineStr"/>
+      <c r="D23" s="19" t="inlineStr"/>
+      <c r="E23" s="19" t="inlineStr"/>
+      <c r="F23" s="29" t="inlineStr"/>
+      <c r="G23" s="29" t="inlineStr"/>
+      <c r="H23" s="29" t="inlineStr"/>
+      <c r="I23" s="21" t="inlineStr"/>
+      <c r="J23" s="21" t="inlineStr"/>
+      <c r="K23" s="30" t="inlineStr"/>
+      <c r="L23" s="31" t="inlineStr"/>
+      <c r="M23" s="31" t="inlineStr"/>
+      <c r="N23" s="31" t="inlineStr"/>
+      <c r="O23" s="32" t="inlineStr"/>
+      <c r="P23" s="32" t="inlineStr"/>
+      <c r="Q23" s="32" t="inlineStr"/>
+      <c r="R23" s="33" t="inlineStr"/>
+      <c r="S23" s="33" t="inlineStr"/>
+      <c r="T23" s="33" t="inlineStr"/>
+      <c r="U23" s="34" t="inlineStr"/>
+      <c r="V23" s="34" t="inlineStr"/>
+      <c r="W23" s="34" t="inlineStr"/>
+      <c r="X23" s="35" t="inlineStr"/>
+      <c r="Y23" s="35" t="inlineStr"/>
+      <c r="Z23" s="36" t="inlineStr"/>
+      <c r="AA23" s="36" t="inlineStr"/>
+      <c r="AB23" s="36" t="inlineStr"/>
+      <c r="AC23" s="36" t="inlineStr"/>
+      <c r="AD23" s="37" t="inlineStr"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="20" t="n"/>
+      <c r="B24" s="29" t="inlineStr"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="20" t="n"/>
+      <c r="M24" s="20" t="n"/>
+      <c r="N24" s="20" t="n"/>
+      <c r="O24" s="20" t="n"/>
+      <c r="P24" s="20" t="n"/>
+      <c r="Q24" s="20" t="n"/>
+      <c r="R24" s="20" t="n"/>
+      <c r="S24" s="20" t="n"/>
+      <c r="T24" s="20" t="n"/>
+      <c r="U24" s="20" t="n"/>
+      <c r="V24" s="20" t="n"/>
+      <c r="W24" s="20" t="n"/>
+      <c r="X24" s="20" t="n"/>
+      <c r="Y24" s="20" t="n"/>
+      <c r="Z24" s="20" t="n"/>
+      <c r="AA24" s="20" t="n"/>
+      <c r="AB24" s="20" t="n"/>
+      <c r="AC24" s="20" t="n"/>
+      <c r="AD24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr"/>
+      <c r="C25" s="19" t="inlineStr"/>
+      <c r="D25" s="19" t="inlineStr"/>
+      <c r="E25" s="19" t="inlineStr"/>
+      <c r="F25" s="29" t="inlineStr"/>
+      <c r="G25" s="29" t="inlineStr"/>
+      <c r="H25" s="29" t="inlineStr"/>
+      <c r="I25" s="21" t="inlineStr"/>
+      <c r="J25" s="21" t="inlineStr"/>
+      <c r="K25" s="30" t="inlineStr"/>
+      <c r="L25" s="31" t="inlineStr"/>
+      <c r="M25" s="31" t="inlineStr"/>
+      <c r="N25" s="31" t="inlineStr"/>
+      <c r="O25" s="32" t="inlineStr"/>
+      <c r="P25" s="32" t="inlineStr"/>
+      <c r="Q25" s="32" t="inlineStr"/>
+      <c r="R25" s="33" t="inlineStr"/>
+      <c r="S25" s="33" t="inlineStr"/>
+      <c r="T25" s="33" t="inlineStr"/>
+      <c r="U25" s="34" t="inlineStr"/>
+      <c r="V25" s="34" t="inlineStr"/>
+      <c r="W25" s="34" t="inlineStr"/>
+      <c r="X25" s="35" t="inlineStr"/>
+      <c r="Y25" s="35" t="inlineStr"/>
+      <c r="Z25" s="36" t="inlineStr"/>
+      <c r="AA25" s="36" t="inlineStr"/>
+      <c r="AB25" s="36" t="inlineStr"/>
+      <c r="AC25" s="36" t="inlineStr"/>
+      <c r="AD25" s="37" t="inlineStr"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="20" t="n"/>
+      <c r="B26" s="29" t="inlineStr"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="20" t="n"/>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="20" t="n"/>
+      <c r="J26" s="20" t="n"/>
+      <c r="K26" s="20" t="n"/>
+      <c r="L26" s="20" t="n"/>
+      <c r="M26" s="20" t="n"/>
+      <c r="N26" s="20" t="n"/>
+      <c r="O26" s="20" t="n"/>
+      <c r="P26" s="20" t="n"/>
+      <c r="Q26" s="20" t="n"/>
+      <c r="R26" s="20" t="n"/>
+      <c r="S26" s="20" t="n"/>
+      <c r="T26" s="20" t="n"/>
+      <c r="U26" s="20" t="n"/>
+      <c r="V26" s="20" t="n"/>
+      <c r="W26" s="20" t="n"/>
+      <c r="X26" s="20" t="n"/>
+      <c r="Y26" s="20" t="n"/>
+      <c r="Z26" s="20" t="n"/>
+      <c r="AA26" s="20" t="n"/>
+      <c r="AB26" s="20" t="n"/>
+      <c r="AC26" s="20" t="n"/>
+      <c r="AD26" s="20" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>※ 상기 안전보건교육 이수 관리대장 작성 기준은 산업안전보건법상의 안전보건교육 이수를 의미함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>※ 상기 교육이수 현황의 경우 산업안전보건법상의 교육실시 결과보고서(기록지)의 증빙이 가능한 교육이수자에 한하여 교육이수현황 기입할 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>※ 특별안전교육 시 2개월 이내 종료되는 일회성작업(단기간 작업) &amp; 연간 총 작업일수 60일 미만작업(간헐적 작업)의 경우 2시간 교육으로 인정가능.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:D4"/>
-    <mergeCell ref="E2:F2"/>
+  <mergeCells count="338">
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Z25:Z26"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="AC23:AC24"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="AB25:AB26"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AD4:AD6"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="AD23:AD24"/>
+    <mergeCell ref="AB21:AB22"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="AC19:AC20"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="AB23:AB24"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="AD17:AD18"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="AD19:AD20"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A29:AD29"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="AA21:AA22"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="Y23:Y24"/>
+    <mergeCell ref="AA23:AA24"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="AD25:AD26"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="X3:AB3"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="AC9:AC10"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="X21:X22"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="AC17:AC18"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="W21:W22"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AB19:AB20"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="N2:AD2"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="Y21:Y22"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="AD21:AD22"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="V23:V24"/>
+    <mergeCell ref="X23:X24"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="U21:U22"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="U23:U24"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="AA25:AA26"/>
+    <mergeCell ref="AC25:AC26"/>
+    <mergeCell ref="A28:AD28"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A30:AD30"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Z11:Z12"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>